--- a/data/trans_orig/IP31KM12_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM12_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51670</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>47334</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>96,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>88,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>52494</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>49637</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>92,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>44636</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>41841</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>45905</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>56251</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>51789</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>58345</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>96,41%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>140</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>108744</t>
+          <t>96306</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103519</t>
+          <t>91976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111067</t>
+          <t>98621</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>463775</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>459464</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>465543</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>606</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>437736</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>430322</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>443543</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>95,24%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>502313</t>
+          <t>410248</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>498094</t>
+          <t>401754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>504167</t>
+          <t>415669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>940049</t>
+          <t>874024</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>931497</t>
+          <t>866018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>945802</t>
+          <t>879885</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2648</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6959</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14096</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8289</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21510</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>22912</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>17066</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>11205</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25585</t>
+          <t>25072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>165120</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>160693</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>143039</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>139413</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>144815</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>95,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>179439</t>
+          <t>144164</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>175735</t>
+          <t>140940</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>146134</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>322477</t>
+          <t>309283</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>316638</t>
+          <t>304777</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>325114</t>
+          <t>311813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1566</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5993</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3147</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1371</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6773</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>9048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>680565</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>674888</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>684044</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>887</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>633268</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>625521</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>639653</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>738002</t>
+          <t>599048</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>731772</t>
+          <t>590631</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>741486</t>
+          <t>605225</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1371270</t>
+          <t>1279613</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1361117</t>
+          <t>1269533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1379267</t>
+          <t>1286966</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6259</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2780</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11936</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>18449</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12064</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26196</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>18663</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>12486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>27080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>17569</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35333</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
